--- a/monitoring_forms/040_email_server_network_traffic_monitoring_log--monitoring_forms.xlsx
+++ b/monitoring_forms/040_email_server_network_traffic_monitoring_log--monitoring_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'http',_'value':_'http'}</t>
+          <t>http</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'HTTP', 'value': 'http'}</t>
+          <t>HTTP</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'smtp',_'value':_'smtp'}</t>
+          <t>smtp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'SMTP', 'value': 'smtp'}</t>
+          <t>SMTP</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'pop3',_'value':_'pop3'}</t>
+          <t>pop3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'POP3', 'value': 'pop3'}</t>
+          <t>POP3</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'imap',_'value':_'imap'}</t>
+          <t>imap</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'IMAP', 'value': 'imap'}</t>
+          <t>IMAP</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'connect',_'value':_'connect'}</t>
+          <t>connect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Connect', 'value': 'connect'}</t>
+          <t>Connect</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'disconnect',_'value':_'disconnect'}</t>
+          <t>disconnect</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Disconnect', 'value': 'disconnect'}</t>
+          <t>Disconnect</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'receive',_'value':_'receive'}</t>
+          <t>receive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Receive', 'value': 'receive'}</t>
+          <t>Receive</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'send',_'value':_'send'}</t>
+          <t>send</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Send', 'value': 'send'}</t>
+          <t>Send</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
